--- a/jobs/uconn-walkways/out/fee_buildup.xlsx
+++ b/jobs/uconn-walkways/out/fee_buildup.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">CD-Level Cost Estimate — Connector Walkway &amp; Chimney Repairs  [A]</t>
   </si>
   <si>
-    <t xml:space="preserve">Kickoff; review 6-sheet CD Review set and photographs; clarification/RFI list to architect</t>
+    <t xml:space="preserve">Kickoff; review 6-sheet CD Review set; clarification/RFI list to architect</t>
   </si>
   <si>
     <t xml:space="preserve">A</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">TOTAL LUMP SUM FEE</t>
   </si>
   <si>
-    <t xml:space="preserve">Locked fee model a9a64e82bcc4: total $9,050. If the buildup is edited, re-run `feeprop price` so the proposal and this workbook stay on one number.</t>
+    <t xml:space="preserve">Locked fee model 77b64f13667b: total $9,050. If the buildup is edited, re-run `feeprop price` so the proposal and this workbook stay on one number.</t>
   </si>
 </sst>
 </file>
@@ -544,7 +544,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C5" s="3" t="s">
         <v>17</v>
       </c>
